--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reading Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reading Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,7 +546,6 @@
           <t>PL units track BC-vs-CB transitions.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>No</t>
@@ -593,13 +598,587 @@
           <t>IFG cross-temporal chunk decoding.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Multiple event segmentation mechanisms in the human brain</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://elifesciences.org/articles/107955</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>★ Paper of the Day</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Using fMRI plus two explicit computational models, this study formally dissociates two candidate mechanisms for placing an event boundary in continuous experience: prediction ERROR (a mismatch between what was expected and what occurred) versus prediction UNCERTAINTY (reduced confidence in the prediction itself) - a distinction your chunk-in-stream task's Start-Target/End-Target/Distractor design could in principle be used to test directly. The two boundary types are not just theoretically distinct but anatomically and temporally dissociable: error-driven boundaries produce early pattern shifts in ventrolateral prefrontal cortex followed by prefrontal/temporal stabilization, whereas uncertainty-driven boundaries are linked instead to parietal dorsal-attention-network shifts with comparatively little subsequent stabilization. Both boundary types nonetheless share a common core multivariate signature with a specific temporal profile - an anterior-temporal pattern shift roughly 12 seconds before the identified boundary, a parietal shift about 4-5 seconds later, then whole-brain pattern stabilization roughly 12 seconds after - giving a concrete multi-stage temporal template for where a boundary-related signal might appear in high-gamma or single-unit data. This speaks directly to your still-open question of whether a chunk boundary (the transition into a memorized target sequence, or the moment a mouse should commit to BC over a distractor) is flagged by a genuine violation-of-expectation signal or by a drop in predictive confidence - two mechanistically distinct signals that would generate different single-unit and LFP predictions in prelimbic cortex or the human frontoparietal network.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Striatal Dopamine at Learned Sequence Boundaries Sustains Birdsong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Xiao, L. et al.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.05.736606</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Phasic striatal dopamine transients occur specifically at the initiation of a learned song sequence (not throughout it), shift progressively earlier - toward sequence onset - as the song matures, and are causally required (via temporally-targeted optogenetic inhibition) for long-term maintenance of the learned sequence. This is a direct precedent for a boundary/onset-locked dopaminergic teaching signal that could interact with your GLM's Module C (slow satiety/time-on-task drift) or with reward-locked events in the go/no-go task, and raises the question of whether the onset of your BC target sequence specifically - as opposed to its constituent chords - carries privileged reward-prediction weight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>An abstract relational map emerges in the human medial prefrontal cortex with consolidation.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Alon B Baram et al.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Current Biology</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42341750/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Using fMRI repetition suppression and RSA, this study finds an abstract relational map of learned graph structure emerging in human medial prefrontal cortex only after several days of consolidation between two scanning sessions, not immediately after learning. That gives a concrete, testable consolidation-timescale prediction for your own prelimbic recordings: if PL is going to show a genuinely position-invariant representation of the BC target (the still-unsolved BC = XBC = XXBC generalization problem), this result suggests that abstraction may only emerge after extended training rather than being present from the first sessions.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Emergence of behavioral tinnitus in gerbils is associated with reduced spontaneous rates in single auditory nerve fibers.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Amarins N Heeringa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42409638/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Single-unit recordings from gerbil auditory nerve fibers show that behaviorally-confirmed tinnitus is associated with a reduction (not increase) in spontaneous firing rate, specific to fibers tuned near the affected frequency band - challenging the simple view that central auditory hyperactivity in tinnitus just reflects peripheral hyperactivity. This is a useful floor-effect consideration when interpreting frequency-specific spontaneous rates in your own auditory-nerve/auditory-cortex single-unit yield, given that your C57BL/6 mice have their own well-characterized progressive high-frequency hearing loss that could similarly confound baseline firing rates with genuine sequence-related changes.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Motor implementation of context- and reward-based urgency regulation during action-oriented decision making.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Thibault Fumery et al.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42409636/</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Behavioral &amp; computational modeling</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Using TMS-measured corticospinal excitability, this study dissociates context-based from reward-based sources of decision urgency and finds they have distinct motor signatures (broad excitability change vs. surround inhibition) that map onto trait impulsivity differently across individuals. This speaks directly to the time-dependent urgency/collapsing-bounds toggle in your leaky-accumulator DDM family - it suggests that a single collapsing-bound term may be conflating two mechanistically separable sources of urgency (task context vs. reward prospect) that could in principle be fit as separate parameters in your model comparison.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A Common Neural Signal of Evidence Accumulation for Perceptual and Mnemonic Decisions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tsvinev, A. et al.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1101/2025.11.13.688140</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Behavioral &amp; computational modeling</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>This EEG study shows the centro-parietal positivity (CPP) - already established as an evidence-accumulation signature in perceptual 2AFC tasks - also tracks accumulation slope in semantic and episodic memory-based decisions, arguing for a domain-general accumulation signal rather than one specific to sensory evidence. That is relevant to whether a shared accumulation signature might link chord-by-chord sensory evidence in your go/no-go task to position-independent template recognition, which bears on your open question of generalizing the target response across different preceding-chord contexts.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Learning regularities in noise engages both neural predictive activity and representational changes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41467-026-74824-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Using MEG and multivariate pattern analysis, this study dissociates two temporally distinct mechanisms for extracting regularities from noise: a rapid predictive-activity response, followed later by a slower change in the underlying stimulus representation itself. This two-stage account is directly relevant to interpreting your mouse behavioral data - it offers a candidate explanation for why distractor confusions might reflect a fast, expectation-like signal (closer to your GLM's trial-history Module B) that is dissociable from a slower-forming, genuinely learned chunk-identity representation (Module A).</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Does stimulus preceding negativity reflect predictions in a somatosensory roving paradigm?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gianluigi Giannini et al.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42409642/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>In a somatosensory roving (oddball) paradigm, this study identifies a stimulus-preceding negativity (SPN) - localized to inferior frontal, fronto-polar, and somatosensory cortex - that scales parametrically with the length of the preceding run of repeated stimuli, i.e., a genuinely anticipatory, pre-stimulus signature of accumulated stimulus history. This is a close conceptual analogue to what you might look for in prelimbic cortex just before a target chord: a prefrontal signal that reflects accumulated evidence from preceding chords rather than only the post-chord discrimination response captured by your current decision-window SDT analysis.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Complementary roles of cell-type-specific plasticity in shaping neocortical dynamics for learning action timing.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Shouvik Majumder et al.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42409803/</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Using cell-type-specific CaMKII manipulations alongside large-scale electrophysiology, this study shows that plasticity in pyramidal-tract (but not intratelencephalic) premotor neurons is specifically required for learning action timing, and that these two projection classes make complementary contributions to population dynamics that anticipate motor timing. This is a useful circuit-dissociation precedent if you ever want to split your Neuropixels yield in prelimbic or auditory cortex by projection class when asking which population is doing the work of anticipating the timing of the target chord within your sequence.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Beyond DSA: Conjugacy-based Comparison of Dynamical Systems</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Prakhar Godara et al.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>arXiv (q-bio.NC)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2607.04493v1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>This methods paper identifies a mathematical gap in Dynamical Similarity Analysis (DSA), a popular method for testing whether two neural population trajectories implement the same underlying computation, and proposes a stricter conjugacy-based alternative that only permits alignments corresponding to genuine state-space bijections. Directly relevant if you use population-geometry or state-space comparisons (e.g., comparing prelimbic vs. auditory cortex trajectories, or comparing sessions/animals) - it flags that DSA-based claims of 'the same dynamics' may not hold up without this stricter criterion.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Development of auditory and spontaneous movement responses to music over the first postnatal year</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://elifesciences.org/articles/107088</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Other notable</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Combining EEG auditory responses with markerless pose-estimation-based movement tracking across the first postnatal year, this study finds that auditory encoding of music emerges early in infancy while structured spontaneous movement to music only appears by 12 months. It's a nice cross-population parallel to your standing interest in treating spontaneous, unprompted movement as a first-class behavioral signal (your GLM's Module C framing) rather than trial-structure noise, and a demonstration of the same continuous pose-estimation approach applied to an auditory paradigm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -651,7 +651,6 @@
           <t>In a somatosensory oddball ('roving') paradigm, the authors find a pre-stimulus anticipatory EEG signal (the stimulus-preceding negativity) that shrinks as a repeated stimulus train gets longer, tracking accumulated stimulus history before the next stimulus even arrives - distinct from the well-studied post-stimulus mismatch response. This is a clean precedent for treating anticipatory, pre-outcome activity as a marker of accumulated sequence history, which is exactly what the decision-window analysis in the mouse sequence-discrimination task is built to isolate (evidence accumulated before the last chord's onset, deliberately separated from reward-consumption licking). It's worth checking whether prelimbic or auditory-cortex recordings carry an analogous pre-chord anticipatory signal that scales with how many chords of the current run a mouse has already heard, independent of the post-chord evoked response.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>No</t>
@@ -719,7 +718,6 @@
           <t>Nelken and Moshitch argue that the standard method for isolating genuine 'deviance sensitivity' or prediction-error signaling in auditory cortex - comparing a deviant tone's response in an oddball sequence to the same tone in a random or ordered control sequence - is not a reliable test: simple adaptation models (narrowly-tuned stimulus-specific adaptation, or network models with firing-rate adaptation and synaptic depression) can reproduce a 'deviant greater than control' pattern with no memory of currently valid regularities and no actual prediction-error computation. This is a direct methodological caution for framing chunk-boundary or novelty responses in the mouse sequence task as evidence of genuine prediction rather than stimulus-specific adaptation, and argues that any claim about auditory or prefrontal cortex 'detecting' a distractor or an out-of-position chord needs an explicit adaptation-model control, not just a deviant-versus-control contrast.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>No</t>
@@ -742,7 +740,6 @@
           <t>Multiple event segmentation mechanisms in the human brain</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Jeffrey M. Zacks</t>
@@ -783,7 +780,6 @@
           <t>Using fMRI and two computational models - one generating event boundaries from prediction error, one from prediction uncertainty - the authors show human-identified event boundaries correspond to a specific temporal sequence of neural pattern changes (early shifts in anterior temporal cortex, then parietal cortex, then whole-brain pattern stabilization), with error-driven and uncertainty-driven boundaries leaving distinguishable neural signatures. This parallels the core theoretical distinction in the human chunk-in-stream task between bottom-up statistical-boundary detection and top-down template-matching detection of a memorized target sequence, and offers a concrete analysis template - fit an error-driven versus an uncertainty-driven boundary model, then look for dissociable pattern-shift signatures - that could be applied to high-gamma or single-unit data around Start-Target and End-Target boundaries in angular gyrus, supramarginal gyrus, or inferior/middle frontal gyrus.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>No</t>
@@ -851,7 +847,6 @@
           <t>In zebra finches, phasic dopamine transients in the song-related basal ganglia circuit shift from marking the later phases of a song sequence to marking sequence onset specifically as the song matures with practice, and optogenetically silencing dopamine right at sequence onset causes the learned song to gradually and severely deteriorate. This shows a sequence boundary - specifically the onset of a learned sequence - is itself a privileged, dopamine-tagged event during natural sequence learning, bearing directly on the mouse sequence-discrimination task's target-onset coding and on the GLM's trial-history module: sequence-initiation itself, not just outcome, may be a distinct dopaminergic signal worth looking for in prelimbic or auditory-cortex recordings around the first chord of a target trial.</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>No</t>
@@ -919,7 +914,6 @@
           <t>The authors show the centro-parietal positivity, an EEG signature of evidence accumulation in perceptual decisions, also appears during memory-based decisions (semantic and episodic judgments) with a build-up rate that scales with evidence strength, response time, and confidence in both domains - arguing for a domain-general accumulate-to-bound signal rather than one specific to sensory evidence. This supports treating evidence accumulation in the leaky-accumulator drift-diffusion model family as a general computational motif rather than needing a separate account for each new evidence type (sensory chord identity versus sequence memory), and is a useful precedent for any future human EEG analogue of accumulation in the chunk-in-stream task's yes/no detection responses.</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>No</t>
@@ -987,7 +981,6 @@
           <t>Using single-pulse TMS to probe corticospinal excitability during a token-based decision task, the authors dissociate two sources of decision 'urgency' - task-context demands versus reward prospects - and show they are implemented through different motor-system mechanisms (broad leg-muscle excitability modulation versus hand-muscle surround inhibition), varying with individual impulsivity traits. This grounds the urgency/collapsing-bound component of the 24-model drift-diffusion family for the mouse sequence task: a context-driven and a reward-driven urgency signal may have genuinely distinct implementations rather than being a single unified urgency term, which could motivate splitting that toggle in a future model variant.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>No</t>
@@ -1030,7 +1023,6 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>2026</t>
@@ -1051,7 +1043,6 @@
           <t>Recording from orbitofrontal-cortex neurons that project specifically to the caudate putamen in rats performing a hidden-reward-state task, the authors show this projection-specific population encodes categorical evidence for the current latent reward state, and perturbing it directly biases the rat's inferred belief about which state it's in. This is a strong precedent for the standing interest in continuous, non-stationary behavioral dynamics and specifically for the GLM's slow-drift module (satiety or time-on-task effects): a state-space-style latent belief has an identifiable, causally manipulable circuit locus, giving a concrete target class - projection-defined orbitofrontal-striatal populations - to consider beyond prelimbic cortex for where a mouse's slow engagement or strategy drift might be represented.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>No</t>
@@ -1119,7 +1110,6 @@
           <t>Recording with two-photon imaging in mouse anterior lateral motor cortex during a context-dependent odor-association task, the authors identify 'contingency neurons' with dual selectivity for context and choice, and show context information reconfigures local circuit routing from sensory input to motor output rather than being abstracted into a context-independent code. This is a useful precedent for the mouse sequence-discrimination task's distractor-context generalization problem - whether a licked response generalizes across different preceding-chord contexts - suggesting mixed context-by-choice selectivity in prelimbic cortex is worth looking for directly, rather than assuming a clean context-invariant sequence code, since that would predict different generalization failure patterns than a fully abstracted representation would.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>No</t>
@@ -1187,7 +1177,6 @@
           <t>Using a model-based functional-connectivity approach in human fMRI, the authors show frontoparietal 'connector hub' regions modulate their coupling with sensory and motor regions differently depending on the specific computational variable at play - entropy (uncertainty before a choice) increases hub coupling with input/output regions, while the inferred task representation separately modulates hub-motor coupling. This gives a template for decomposing frontoparietal integration into distinct, computationally-defined coupling regimes rather than a single static property, relevant to the human chunk-in-stream work's inferior and middle frontal gyrus recordings if characterizing how top-down template information and bottom-up statistical evidence are routed differently through the same frontoparietal sites during detection.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1255,7 +1244,6 @@
           <t>Combining a graph-learning task with fMRI repetition suppression and representational similarity analysis, the authors find an abstract relational map of learned associations emerges in the medial prefrontal cortex only across two scanning sessions separated by several days, not within a single session - direct evidence that structural abstraction away from sensory detail is a slow, multi-day cortical process in humans, mirroring prior rodent reports. This bears on the timeline of the human chunk-in-stream participant's seven recording sessions: if template or chunk representations reorganize similarly across days, representational similarity analysis across sessions (rather than only within-session decoding) may be necessary to detect true structural learning in angular gyrus, supramarginal gyrus, or frontal recordings, especially on the top-down template-matching side of the task.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1323,7 +1311,6 @@
           <t>Combining fMRI in healthy adults with behavioral testing of patients with severe aphasia from extensive damage to language brain areas, the authors find logical reasoning tasks do not engage the language network and that aphasic patients perform normally on logic tasks despite their linguistic impairment - evidence that inductive and deductive reasoning recruit the domain-general 'multiple demand' network rather than language machinery itself. This is a useful independent data point for framing the human chunk-in-stream participant's profile (severely impaired comprehension, largely spared repetition): it suggests general inductive/logical reasoning capacity may be dissociable from the comprehension deficit, relevant to deciding how much general-cognitive versus specifically linguistic capacity to assume is intact when designing statistical-learning versus template-matching conditions for this participant.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1391,7 +1378,6 @@
           <t>Using multisite local field potential recordings across mouse auditory cortex and medial prefrontal cortex, the authors show oxytocin selectively boosts auditory-cortex and prefrontal responses to infant calls while suppressing baseline spontaneous activity (raising signal-to-noise), and specifically increases low-theta phase coupling and directional connectivity from auditory cortex to prefrontal cortex during rest. This is a directly relevant precedent for the prelimbic/auditory-cortex Neuropixels recordings in the mouse sequence task: it demonstrates using directional, Granger-causal connectivity measures between exactly these two regions to characterize how auditory information is gated into prefrontal cortex, and raises neuromodulatory state as a candidate source of session-to-session variability in auditory-to-prelimbic coupling.</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1459,13 +1445,420 @@
           <t>Combining EEG and markerless pose-estimation kinematics in 79 infants aged 3, 6, and 12 months listening to music, the authors find enhanced auditory neural responses to structured versus shuffled music are present from 3 months, but complex, structured spontaneous movement to music only emerges by 12 months, with no age group showing tightly coordinated movement. This is an independent data point for the standing interest in treating spontaneous, continuous movement as real behavioral data rather than a nuisance to filter out (the same philosophy behind the GLM's slow-drift module), and the pose-estimation approach used here for quantifying unprompted movement is directly the kind of continuous-behavior-tracking method relevant to that standing interest, even outside the auditory-sequence-discrimination context specifically.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Learning regularities in noise engages both neural predictive activity and representational changes.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Coumarane Tirou et al.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Romain Quentin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Université Claude Bernard Lyon 1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42409831/</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Using MEG during a visuomotor task, Tirou et al. show that learning non-adjacent temporal dependencies embedded in noise unfolds in two dissociable stages: fast-emerging predictive activity (stimulus-specific patterns appearing before stimulus onset, preceding any behavioral improvement) followed by a slower build-up of representational similarity between the statistically-linked, non-adjacent elements themselves. This maps onto the distinction your mouse sequence-discrimination task needs to draw between anticipatory decision-window discrimination (your d-prime measure) and slower session-level representational learning of which chords co-occur — it's a concrete two-stage hypothesis worth testing against your own early-versus-late-session data. Németh is on your watch list, and this is a direct hit on 'non-adjacent dependencies,' one of your explicitly listed core topics.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Multiple event segmentation mechanisms in the human brain.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tan T Nguyen et al.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Jeffrey M Zacks</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42411461/</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Nguyen et al. use fMRI plus two computational models — one driven by prediction error, one by prediction uncertainty — to show that human-perceived event boundaries in continuous experience are the product of two temporally and anatomically distinct signals: an early error-driven shift in prefrontal and anterior temporal regions, and a separate, later uncertainty-driven shift in parietal dorsal-attention regions. This is a useful formal vocabulary for your human chunk-in-stream task's distractor design: your near-miss distractors (temporal reversals, circular shifts, neighbour mutations) plausibly drive error-type boundary signals, while unrelated background chunks may lean more on the uncertainty-type signal, and this gives you a specific way to test that split in your own high-gamma or single-unit data. It's fMRI rather than intracranial, so treat the region-level claims as a coarse map to test against, not a settled circuit.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hippocampal engrams configure prefrontal context representations to guide flexible decisions</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Julian, J. B. et al.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Carlos Brody</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Princeton University</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.06.732916</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Julian, Kaminsky, Tank &amp; Brody combine hippocampal engram tagging/reactivation with large-scale recordings in mouse medial prefrontal cortex during a context-dependent task-switching paradigm, showing that reactivating a hippocampal engram for a given context reinstates that context's representation in prefrontal cortex within hundreds of milliseconds and causally redirects which stimulus-response rule the animal applies. This is a direct precedent for the kind of prelimbic-cortex, context-dependent population coding you record in your own go/no-go sequence task — it demonstrates that a fast, engram-linked context signal in prefrontal cortex can determine which decision rule governs an upcoming trial, which is exactly the kind of session-to-session context-switching your adaptive distractor-difficulty algorithm implicitly probes. Carlos Brody is on your watch list.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brain2voice 2.0: High-performance voice synthesis brain-computer interface</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Maitreyee Wairagkar et al.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sergey D. Stavisky</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>University of California, Davis</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>bioRxiv (Cold Spring Harbor Laboratory)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.06.30.735633</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Language, stroke &amp; BCI</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Wairagkar et al. (the BrainGate/UC Davis group) introduce brain2voice 2.0, a Transformer-based decoder that synthesizes real-time, intelligible voice directly from intracortical neural signals, cutting listener transcription word-error-rate from 43.75% to 5.24% — an eight-fold intelligibility improvement over the prior state of the art on the same benchmark dataset. This is squarely in your clinical/translational tier: it's a concrete picture of what a chronic intracortical array in a language-impaired participant like yours could eventually support beyond detection tasks, and their phoneme-aligned, causal real-time decoding objective is worth comparing against how you extract trial-aligned high-gamma and single-unit features in your chunk-in-stream task.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Structural connectivity of auditory-linguistic brain networks predicts success in speech categorization and listening in noise</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Rizzi, R. et al.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Gavin M. Bidelman</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Indiana University Bloomington</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.06.736789</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Language, stroke &amp; BCI</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Rizzi, Stirn, Eisenhut &amp; Bidelman use diffusion-weighted imaging and tractography to show that individual differences in how gradiently versus discretely people categorize speech sounds, and how well they understand speech in noise, track with white-matter density in the arcuate fasciculus and brainstem-cortical auditory pathways, plus cortical thickness in right superior temporal gyrus. It's a non-invasive structural correlate rather than a mechanistic account, but it's a reminder that the statistical-learning-versus-top-down-template-matching distinction you use to frame your chunk-in-stream task has a documented individual-differences anatomical signature in the human auditory-linguistic pathway — a reason to consider collecting structural scans alongside electrophysiology in future human sessions.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Development of auditory and spontaneous movement responses to music over the first postnatal year.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Trinh Nguyen et al.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Giacomo Novembre</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Italian Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42411060/</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Other notable</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Nguyen et al. record EEG and markerless pose-estimated body movement simultaneously in 79 infants aged 3-12 months listening to music, finding that auditory encoding of musical structure is present from 3 months, but structured, music-driven movement (rocking, swaying, clapping-like patterns) only emerges by 12 months and even then is not beat-synchronized. It's a developmental study far from your own paradigms, but it's a clean example of your 'continuous behavior as ground truth' standing interest — treating spontaneous movement as a real, quantifiable readout of internal auditory processing rather than noise around a trial structure, in the same spirit as your GLM's slow-drift module for licking behavior.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1512,7 +1512,6 @@
           <t>Using MEG during a visuomotor task, Tirou et al. show that learning non-adjacent temporal dependencies embedded in noise unfolds in two dissociable stages: fast-emerging predictive activity (stimulus-specific patterns appearing before stimulus onset, preceding any behavioral improvement) followed by a slower build-up of representational similarity between the statistically-linked, non-adjacent elements themselves. This maps onto the distinction your mouse sequence-discrimination task needs to draw between anticipatory decision-window discrimination (your d-prime measure) and slower session-level representational learning of which chords co-occur — it's a concrete two-stage hypothesis worth testing against your own early-versus-late-session data. Németh is on your watch list, and this is a direct hit on 'non-adjacent dependencies,' one of your explicitly listed core topics.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>No</t>
@@ -1580,7 +1579,6 @@
           <t>Nguyen et al. use fMRI plus two computational models — one driven by prediction error, one by prediction uncertainty — to show that human-perceived event boundaries in continuous experience are the product of two temporally and anatomically distinct signals: an early error-driven shift in prefrontal and anterior temporal regions, and a separate, later uncertainty-driven shift in parietal dorsal-attention regions. This is a useful formal vocabulary for your human chunk-in-stream task's distractor design: your near-miss distractors (temporal reversals, circular shifts, neighbour mutations) plausibly drive error-type boundary signals, while unrelated background chunks may lean more on the uncertainty-type signal, and this gives you a specific way to test that split in your own high-gamma or single-unit data. It's fMRI rather than intracranial, so treat the region-level claims as a coarse map to test against, not a settled circuit.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>No</t>
@@ -1648,7 +1646,6 @@
           <t>Julian, Kaminsky, Tank &amp; Brody combine hippocampal engram tagging/reactivation with large-scale recordings in mouse medial prefrontal cortex during a context-dependent task-switching paradigm, showing that reactivating a hippocampal engram for a given context reinstates that context's representation in prefrontal cortex within hundreds of milliseconds and causally redirects which stimulus-response rule the animal applies. This is a direct precedent for the kind of prelimbic-cortex, context-dependent population coding you record in your own go/no-go sequence task — it demonstrates that a fast, engram-linked context signal in prefrontal cortex can determine which decision rule governs an upcoming trial, which is exactly the kind of session-to-session context-switching your adaptive distractor-difficulty algorithm implicitly probes. Carlos Brody is on your watch list.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1716,7 +1713,6 @@
           <t>Wairagkar et al. (the BrainGate/UC Davis group) introduce brain2voice 2.0, a Transformer-based decoder that synthesizes real-time, intelligible voice directly from intracortical neural signals, cutting listener transcription word-error-rate from 43.75% to 5.24% — an eight-fold intelligibility improvement over the prior state of the art on the same benchmark dataset. This is squarely in your clinical/translational tier: it's a concrete picture of what a chronic intracortical array in a language-impaired participant like yours could eventually support beyond detection tasks, and their phoneme-aligned, causal real-time decoding objective is worth comparing against how you extract trial-aligned high-gamma and single-unit features in your chunk-in-stream task.</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>No</t>
@@ -1784,7 +1780,6 @@
           <t>Rizzi, Stirn, Eisenhut &amp; Bidelman use diffusion-weighted imaging and tractography to show that individual differences in how gradiently versus discretely people categorize speech sounds, and how well they understand speech in noise, track with white-matter density in the arcuate fasciculus and brainstem-cortical auditory pathways, plus cortical thickness in right superior temporal gyrus. It's a non-invasive structural correlate rather than a mechanistic account, but it's a reminder that the statistical-learning-versus-top-down-template-matching distinction you use to frame your chunk-in-stream task has a documented individual-differences anatomical signature in the human auditory-linguistic pathway — a reason to consider collecting structural scans alongside electrophysiology in future human sessions.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>No</t>
@@ -1852,13 +1847,1020 @@
           <t>Nguyen et al. record EEG and markerless pose-estimated body movement simultaneously in 79 infants aged 3-12 months listening to music, finding that auditory encoding of musical structure is present from 3 months, but structured, music-driven movement (rocking, swaying, clapping-like patterns) only emerges by 12 months and even then is not beat-synchronized. It's a developmental study far from your own paradigms, but it's a clean example of your 'continuous behavior as ground truth' standing interest — treating spontaneous movement as a real, quantifiable readout of internal auditory processing rather than noise around a trial structure, in the same spirit as your GLM's slow-drift module for licking behavior.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Multiple event segmentation mechanisms in the human brain.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Tan T Nguyen et al.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Jeffrey M Zacks</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42411461/</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>★ Paper of the Day</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Using fMRI and computational modeling, this group formally dissociates two distinct triggers for perceived event boundaries in continuous experience: high prediction error (mismatch between expected and observed information) and high prediction uncertainty (reduced confidence in the prediction itself) — accounts that prior work had largely conflated. The two boundary types produce distinguishable spatiotemporal signatures: error-driven boundaries evoke early pattern shifts in ventrolateral prefrontal areas followed by prefrontal/temporal stabilization, while uncertainty-driven boundaries evoke shifts confined to parietal regions of the dorsal attention network with minimal subsequent stabilization. Across boundary types there is a conserved temporal cascade — anterior temporal pattern shifts first (about 12 seconds before the boundary), then parietal shifts, then whole-brain pattern stabilization afterward — suggesting event segmentation is a distributed, sequenced process rather than a single mechanism firing at one moment. This gives chunking a genuine operational, two-factor definition (error versus uncertainty) with dissociable neural signatures, rather than treating 'a boundary was detected' as a single undifferentiated event — directly useful for thinking about what a chunk boundary in an auditory stream actually is, computationally.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Environment geometry alters sequential route learning and its integration into cognitive maps.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jaida Long et al.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Thackery Brown</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42414280/</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>This study shows that serial-order effects in route learning combine additively with environmental-geometry effects on spatial memory, with the worst location memory occurring at the end of routes through the most irregular (trapezoid) environments. That additive combination of a position-in-sequence effect and an environment-shape effect is a useful precedent for the location-sequence version of the mouse task you're currently developing, where sequence elements are defined by spatial position rather than pitch: it suggests position-dependent memory effects (like the primacy bias you're probing in Protocol 8) and physical/geometric context could combine rather than trade off, which becomes testable once that task has enough conditions to separate the two factors.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Neuronal dynamics, timing, and flow of sensory and choice-related information in auditory-prefrontal circuitry</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bruno B. Averbeck</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>National Institute of Mental Health (NIH)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41467-026-75349-2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Recording from macaque auditory cortex and prefrontal cortex during an auditory decision task, this group shows that raw sensory information flows in the feedforward direction (auditory cortex to prefrontal cortex) while choice-related information flows bidirectionally between the two regions — a clean dissociation of what propagates forward versus what involves both areas jointly. This is close to a direct analogue of the mouse sequence-discrimination task's core question of how auditory cortex and prelimbic cortex jointly support the go/no-go decision: the directional/timing analysis here is a template for asking whether your own Neuropixels recordings from prelimbic and auditory cortex show the same feedforward-sensory/bidirectional-choice pattern around the decision window at the last chord.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Medial prefrontal cortex encodes but is not required to generate goal-directed actions under threat.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Muhammad S Sajid et al.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Manuel A Castro-Alamancos</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42417528/</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Using fiber photometry, single-cell calcium imaging, and optogenetic inhibition in mouse medial prefrontal cortex during learned avoidance tasks, this study finds that GABAergic medial-prefrontal neurons encode cues, actions, and outcomes with increasing task complexity, but silencing that cortex has minimal effect on learning or performance — its activity reflects movement and evaluative signals rather than causally generating the action. That's a direct methodological caution for the prelimbic-cortex recordings in the mouse sequence-discrimination task: a region can carry rich task-related information, which your prelimbic Neuropixels data will likely also show, without being causally necessary for the behavior, so any causal claim about prelimbic cortex driving the go/no-go decision would need its own inactivation experiment, not just encoding strength.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Predictive acoustical processing in human cortical layers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lonike K. Faes et al.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Federico De Martino</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Maastricht University</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41467-026-73540-z</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Using laminar-resolution fMRI during a cascading auditory oddball paradigm, this study (co-authored by watch-listed predictive-processing researcher Ryszard Auksztulewicz) localizes prediction-error signals to superficial cortical layers of planum polare and middle layers of lateral temporal cortex, with model-updating tied to deep-layer activity — evidence for a layer-specific implementation of hierarchical predictive coding in human auditory cortex. This gives a concrete laminar target for the statistical-learning side of the human chunk-in-stream task: if high-gamma responses during the statistical-background-variation stage of that task (where bottom-up pattern extraction and top-down template matching are meant to dissociate) show a similar superficial-versus-deep split, that would support reading prediction-error and model-update signals off different cortical depths rather than treating high-gamma as one undifferentiated regularity signal.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Age-related changes in behavioural and neural variability in a decision-making task</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fenying Zang et al.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Anne E Urai</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Leiden University</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41467-026-74227-1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Behavioral &amp; computational modeling</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Recording over 18,000 neurons across 16 brain regions in young and aged mice performing a visual decision task, this group shows that aging increases post-stimulus neural variability (Fano factor) and reduces stimulus-induced variability quenching, with region-specific direction — higher firing in cortex and striatum, lower in thalamus. This is a large-scale demonstration of exactly the kind of continuous, state-dependent framing your GLM Module C (slow drift from satiety or time-on-task) is trying to capture in the mouse sequence-discrimination task: variability-quenching metrics like theirs could be applied session-by-session to your prelimbic and auditory cortex recordings to ask whether within-session drift in engagement shows up as a comparable loss of stimulus-locked variability reduction, independent of your existing hit/false-alarm-based Module C features.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Learning regularities in noise engages both neural predictive activity and representational changes</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Coumarane Tirou et al.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Romain Quentin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Université Claude Bernard Lyon 1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41467-026-74824-0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Using MEG during a visuomotor task with non-adjacent temporal dependencies embedded in noise, this study (with watch-listed statistical-learning researcher Dezső Németh as a co-author) dissociates two temporally separate learning mechanisms: a fast-emerging neural predictive-activity signal that appears before behavioral improvement, and a slower-building representational change that increases neural pattern similarity between the statistically dependent elements. This maps directly onto the bottom-up-statistical-learning-versus-top-down-template-matching framing at the core of the human chunk-in-stream task's design, and gives a concrete analysis template — pre-stimulus predictive decoding versus pattern-similarity growth across sessions — for separating those two processes in your own high-gamma and single-unit data as target sequences move toward full multi-template scene analysis.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Using hierarchical statistical learning models to model individual statistical learning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hanna Ringer et al.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tatsuya Daikoku</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>University of Tokyo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>arXiv (q-bio.NC)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2607.05822v1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>This preprint fits a Hierarchical Bayesian Statistical Learning model to individual EEG-derived learning trajectories as adults with and without dyslexia listen to structured tone sequences, and shows the model's simulated sequences closely match what participants actually generated — a working proof of concept for individual-level generative models of sequence learning. It's a useful methodological cousin to your own per-session model-fitting toolchain (the 24-model leaky-accumulator family fit by differential evolution, plus the tiered GLM strategy models): both try to recover an individual's latent learning process from sequence behavior, and this hierarchical Bayesian framing is worth comparing against your AICc/Akaike-weight model selection as an alternative way to handle per-mouse or per-session variability in the tone-sequence version of your task.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Multi-network Topology Underlying Individual Language Learning Success</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Gangyi Feng</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Chinese University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR, China</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>http://www.jneurosci.org/cgi/content/short/46/27/e2205252026?rss=1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Language, stroke &amp; BCI</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Using multimodal neuroimaging before and during seven days of artificial-language training across six tasks (auditory/speech categories, words, morphosyntax, sentence structure), this study finds that individual differences in learning outcome and rate are best predicted by the local efficiency of the dorsal-attention and frontoparietal control networks, not classic frontotemporal language regions alone. That distributed-network account of language-learning success is a relevant frame for the top-down template-matching side of the human chunk-in-stream task, particularly at the participant's frontoparietal recording sites (inferior and middle frontal gyrus): if attention/control-network engagement predicts how quickly a new stimulus class is learned, that argues for tracking frontoparietal signal quality across sessions when comparing performance across the harmonic-chord, vowel, and syllable stimulus classes.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Neural decoding of speech using deep neural ensembles</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seonghyun Yoon et al.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Francis R Willett</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.06.02.729705</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Language, stroke &amp; BCI</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>In a closed-loop test with a participant implanted with bilateral intracortical microelectrode arrays, this group shows that ensembling multiple independently trained decoders reduces speech brain-computer-interface word-error rate from 33.7% to 26.0%, and introduces a cheaper pseudo-ensembling method (test-time augmentation on a single decoder) that captures much of the benefit without the full computational cost. This is directly relevant to the human chunk-in-stream work's broader translational context — intracortical decoding in a person with severe language impairment — and the pseudo-ensembling trick is a concretely reusable idea for your own single-unit and high-gamma decoding pipelines in angular gyrus, supramarginal gyrus, and frontal sites, where training data per session is similarly limited by session count.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KIASORT: Knowledge-Integrated Automated Spike Sorting for Geometry-Free Neuron Tracking</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Kianoush Banaie Boroujeni</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Princeton University</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>http://www.jneurosci.org/cgi/content/short/46/27/e1594252026?rss=1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>KIASORT is a new geometry-free spike-sorting algorithm that tracks each neuron's waveform drift independently rather than assuming a shared one-dimensional drift model across the probe, and the authors show it outperforms Kilosort4 on ground-truth benchmarks with heterogeneous per-neuron drift, validated on both primate and mouse data. Since your mouse Neuropixels 2.0 recordings from prelimbic and auditory cortex are currently sorted with Kilosort and drift is a known problem for long recordings, this is a direct pipeline-upgrade candidate worth benchmarking against your existing output — particularly if you've noticed unit-identity or waveform instability across a session, which per-neuron drift tracking is specifically designed to fix.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Neuropixels Opto: combining high-resolution electrophysiology and optogenetics</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Anna A. Lakunina et al.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Matteo Carandini</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nature Methods</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41592-026-03076-z</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>This paper introduces Neuropixels Opto, a probe integrating 960 recording sites with 28 independently addressable light emitters on the same shank, enabling spatially targeted optogenetic activation or silencing at specific cortical depths during high-density recording, and demonstrates efficient two-cell-type optotagging in mouse striatum. For the mouse sequence-discrimination task, where you already use Neuropixels 2.0 in prelimbic and auditory cortex, this would let you causally test which cortical layer or cell type carries the decision signal you currently only characterize correlationally — for instance, silencing superficial versus deep layers during the decision window to ask whether the prelimbic signal is more like the movement/evaluative activity described in today's medial-prefrontal-cortex threat paper, or a genuine causal driver of the go/no-go choice.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quantifying Entrainment Evidence: A Comparison of Frequentist and Bayesian Approaches for Information Processing Pathway Maps</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kaibo Zhang et al.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Andrew Thwaites</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>arXiv (q-bio.NC)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2607.06284v1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>This preprint directly compares frequentist null-hypothesis testing against a Bayesian evidence-accumulation framework for adjudicating between competing computational models of an auditory processing pathway (loudness processing), arguing the Bayesian approach better handles collinear/competing models and yields a genuine measure of relative evidence rather than a simple reject/fail-to-reject decision. This is a close methodological parallel to your own model-selection practice — AICc and Akaike weights across your 24 nested drift-diffusion models, and cross-validated information gain for the GLM strategy models — and is worth reading as a check on whether a fully Bayesian evidence framework would handle collinearity between your structurally similar nested models (for instance leaky integration versus urgency) better than AICc currently does.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>The structure of correlated variability reflects task-relevant information in sensory neurons.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ramanujan Srinath et al.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Marlene R Cohen</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>University of Chicago</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PNAS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42412944/</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>This group shows, via a circuit model plus multi-area population recordings, that the dominant axis of shared trial-to-trial variability in sensory neurons consistently aligns with task-relevant stimulus features and action plans, and that this shared-variability axis predicts the behavioral effect of microstimulation — reframing correlated variability as something that reveals rather than obscures the information sent downstream. This is a useful population-analysis framing for your own auditory cortex and prelimbic Neuropixels data: rather than treating trial-to-trial variability purely as noise to average out in dPCA or mixed-selectivity analyses, it's worth checking whether the low-dimensional axis of shared variability in your target-chord-evoked responses aligns with the decision-relevant dimension your GLM Module A features already isolate.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Development of auditory and spontaneous movement responses to music over the first postnatal year.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Trinh Nguyen et al.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Giacomo Novembre</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Italian Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42411060/</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Other notable</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>This group simultaneously recorded EEG and markerless-pose-estimation-based body kinematics from 79 infants (3, 6, and 12 months) listening to music, finding that enhanced neural auditory responses to music are present from 3 months, but structured, complex movement patterns in response to music only emerge by 12 months — auditory encoding and motor response to sound develop on different timescales. This sits squarely inside your standing interest in continuous, pose-estimation-based behavioral quantification rather than per-trial outcomes, and offers a conceptual mirror for the mouse work: it's a reminder that a subject can show clear neural sensitivity to a sound sequence's structure well before that sensitivity is expressed in structured movement — relevant when interpreting mice that discriminate the target sequence from its reordered distractor in evoked activity but haven't yet generalized that to a reliable licking response, especially under the currently-running slow-pacing protocol.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1986,7 +1986,6 @@
           <t>This study shows that serial-order effects in route learning combine additively with environmental-geometry effects on spatial memory, with the worst location memory occurring at the end of routes through the most irregular (trapezoid) environments. That additive combination of a position-in-sequence effect and an environment-shape effect is a useful precedent for the location-sequence version of the mouse task you're currently developing, where sequence elements are defined by spatial position rather than pitch: it suggests position-dependent memory effects (like the primacy bias you're probing in Protocol 8) and physical/geometric context could combine rather than trade off, which becomes testable once that task has enough conditions to separate the two factors.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>No</t>
@@ -2009,7 +2008,6 @@
           <t>Neuronal dynamics, timing, and flow of sensory and choice-related information in auditory-prefrontal circuitry</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>Bruno B. Averbeck</t>
@@ -2050,7 +2048,6 @@
           <t>Recording from macaque auditory cortex and prefrontal cortex during an auditory decision task, this group shows that raw sensory information flows in the feedforward direction (auditory cortex to prefrontal cortex) while choice-related information flows bidirectionally between the two regions — a clean dissociation of what propagates forward versus what involves both areas jointly. This is close to a direct analogue of the mouse sequence-discrimination task's core question of how auditory cortex and prelimbic cortex jointly support the go/no-go decision: the directional/timing analysis here is a template for asking whether your own Neuropixels recordings from prelimbic and auditory cortex show the same feedforward-sensory/bidirectional-choice pattern around the decision window at the last chord.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>No</t>
@@ -2118,7 +2115,6 @@
           <t>Using fiber photometry, single-cell calcium imaging, and optogenetic inhibition in mouse medial prefrontal cortex during learned avoidance tasks, this study finds that GABAergic medial-prefrontal neurons encode cues, actions, and outcomes with increasing task complexity, but silencing that cortex has minimal effect on learning or performance — its activity reflects movement and evaluative signals rather than causally generating the action. That's a direct methodological caution for the prelimbic-cortex recordings in the mouse sequence-discrimination task: a region can carry rich task-related information, which your prelimbic Neuropixels data will likely also show, without being causally necessary for the behavior, so any causal claim about prelimbic cortex driving the go/no-go decision would need its own inactivation experiment, not just encoding strength.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>No</t>
@@ -2186,7 +2182,6 @@
           <t>Using laminar-resolution fMRI during a cascading auditory oddball paradigm, this study (co-authored by watch-listed predictive-processing researcher Ryszard Auksztulewicz) localizes prediction-error signals to superficial cortical layers of planum polare and middle layers of lateral temporal cortex, with model-updating tied to deep-layer activity — evidence for a layer-specific implementation of hierarchical predictive coding in human auditory cortex. This gives a concrete laminar target for the statistical-learning side of the human chunk-in-stream task: if high-gamma responses during the statistical-background-variation stage of that task (where bottom-up pattern extraction and top-down template matching are meant to dissociate) show a similar superficial-versus-deep split, that would support reading prediction-error and model-update signals off different cortical depths rather than treating high-gamma as one undifferentiated regularity signal.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>No</t>
@@ -2254,7 +2249,6 @@
           <t>Recording over 18,000 neurons across 16 brain regions in young and aged mice performing a visual decision task, this group shows that aging increases post-stimulus neural variability (Fano factor) and reduces stimulus-induced variability quenching, with region-specific direction — higher firing in cortex and striatum, lower in thalamus. This is a large-scale demonstration of exactly the kind of continuous, state-dependent framing your GLM Module C (slow drift from satiety or time-on-task) is trying to capture in the mouse sequence-discrimination task: variability-quenching metrics like theirs could be applied session-by-session to your prelimbic and auditory cortex recordings to ask whether within-session drift in engagement shows up as a comparable loss of stimulus-locked variability reduction, independent of your existing hit/false-alarm-based Module C features.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>No</t>
@@ -2322,7 +2316,6 @@
           <t>Using MEG during a visuomotor task with non-adjacent temporal dependencies embedded in noise, this study (with watch-listed statistical-learning researcher Dezső Németh as a co-author) dissociates two temporally separate learning mechanisms: a fast-emerging neural predictive-activity signal that appears before behavioral improvement, and a slower-building representational change that increases neural pattern similarity between the statistically dependent elements. This maps directly onto the bottom-up-statistical-learning-versus-top-down-template-matching framing at the core of the human chunk-in-stream task's design, and gives a concrete analysis template — pre-stimulus predictive decoding versus pattern-similarity growth across sessions — for separating those two processes in your own high-gamma and single-unit data as target sequences move toward full multi-template scene analysis.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>No</t>
@@ -2390,7 +2383,6 @@
           <t>This preprint fits a Hierarchical Bayesian Statistical Learning model to individual EEG-derived learning trajectories as adults with and without dyslexia listen to structured tone sequences, and shows the model's simulated sequences closely match what participants actually generated — a working proof of concept for individual-level generative models of sequence learning. It's a useful methodological cousin to your own per-session model-fitting toolchain (the 24-model leaky-accumulator family fit by differential evolution, plus the tiered GLM strategy models): both try to recover an individual's latent learning process from sequence behavior, and this hierarchical Bayesian framing is worth comparing against your AICc/Akaike-weight model selection as an alternative way to handle per-mouse or per-session variability in the tone-sequence version of your task.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>No</t>
@@ -2413,7 +2405,6 @@
           <t>Multi-network Topology Underlying Individual Language Learning Success</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>Gangyi Feng</t>
@@ -2454,7 +2445,6 @@
           <t>Using multimodal neuroimaging before and during seven days of artificial-language training across six tasks (auditory/speech categories, words, morphosyntax, sentence structure), this study finds that individual differences in learning outcome and rate are best predicted by the local efficiency of the dorsal-attention and frontoparietal control networks, not classic frontotemporal language regions alone. That distributed-network account of language-learning success is a relevant frame for the top-down template-matching side of the human chunk-in-stream task, particularly at the participant's frontoparietal recording sites (inferior and middle frontal gyrus): if attention/control-network engagement predicts how quickly a new stimulus class is learned, that argues for tracking frontoparietal signal quality across sessions when comparing performance across the harmonic-chord, vowel, and syllable stimulus classes.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>No</t>
@@ -2497,7 +2487,6 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>2026</t>
@@ -2518,7 +2507,6 @@
           <t>In a closed-loop test with a participant implanted with bilateral intracortical microelectrode arrays, this group shows that ensembling multiple independently trained decoders reduces speech brain-computer-interface word-error rate from 33.7% to 26.0%, and introduces a cheaper pseudo-ensembling method (test-time augmentation on a single decoder) that captures much of the benefit without the full computational cost. This is directly relevant to the human chunk-in-stream work's broader translational context — intracortical decoding in a person with severe language impairment — and the pseudo-ensembling trick is a concretely reusable idea for your own single-unit and high-gamma decoding pipelines in angular gyrus, supramarginal gyrus, and frontal sites, where training data per session is similarly limited by session count.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>No</t>
@@ -2541,7 +2529,6 @@
           <t>KIASORT: Knowledge-Integrated Automated Spike Sorting for Geometry-Free Neuron Tracking</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>Kianoush Banaie Boroujeni</t>
@@ -2582,7 +2569,6 @@
           <t>KIASORT is a new geometry-free spike-sorting algorithm that tracks each neuron's waveform drift independently rather than assuming a shared one-dimensional drift model across the probe, and the authors show it outperforms Kilosort4 on ground-truth benchmarks with heterogeneous per-neuron drift, validated on both primate and mouse data. Since your mouse Neuropixels 2.0 recordings from prelimbic and auditory cortex are currently sorted with Kilosort and drift is a known problem for long recordings, this is a direct pipeline-upgrade candidate worth benchmarking against your existing output — particularly if you've noticed unit-identity or waveform instability across a session, which per-neuron drift tracking is specifically designed to fix.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>No</t>
@@ -2650,7 +2636,6 @@
           <t>This paper introduces Neuropixels Opto, a probe integrating 960 recording sites with 28 independently addressable light emitters on the same shank, enabling spatially targeted optogenetic activation or silencing at specific cortical depths during high-density recording, and demonstrates efficient two-cell-type optotagging in mouse striatum. For the mouse sequence-discrimination task, where you already use Neuropixels 2.0 in prelimbic and auditory cortex, this would let you causally test which cortical layer or cell type carries the decision signal you currently only characterize correlationally — for instance, silencing superficial versus deep layers during the decision window to ask whether the prelimbic signal is more like the movement/evaluative activity described in today's medial-prefrontal-cortex threat paper, or a genuine causal driver of the go/no-go choice.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>No</t>
@@ -2718,7 +2703,6 @@
           <t>This preprint directly compares frequentist null-hypothesis testing against a Bayesian evidence-accumulation framework for adjudicating between competing computational models of an auditory processing pathway (loudness processing), arguing the Bayesian approach better handles collinear/competing models and yields a genuine measure of relative evidence rather than a simple reject/fail-to-reject decision. This is a close methodological parallel to your own model-selection practice — AICc and Akaike weights across your 24 nested drift-diffusion models, and cross-validated information gain for the GLM strategy models — and is worth reading as a check on whether a fully Bayesian evidence framework would handle collinearity between your structurally similar nested models (for instance leaky integration versus urgency) better than AICc currently does.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>No</t>
@@ -2786,7 +2770,6 @@
           <t>This group shows, via a circuit model plus multi-area population recordings, that the dominant axis of shared trial-to-trial variability in sensory neurons consistently aligns with task-relevant stimulus features and action plans, and that this shared-variability axis predicts the behavioral effect of microstimulation — reframing correlated variability as something that reveals rather than obscures the information sent downstream. This is a useful population-analysis framing for your own auditory cortex and prelimbic Neuropixels data: rather than treating trial-to-trial variability purely as noise to average out in dPCA or mixed-selectivity analyses, it's worth checking whether the low-dimensional axis of shared variability in your target-chord-evoked responses aligns with the decision-relevant dimension your GLM Module A features already isolate.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>No</t>
@@ -2854,13 +2837,344 @@
           <t>This group simultaneously recorded EEG and markerless-pose-estimation-based body kinematics from 79 infants (3, 6, and 12 months) listening to music, finding that enhanced neural auditory responses to music are present from 3 months, but structured, complex movement patterns in response to music only emerge by 12 months — auditory encoding and motor response to sound develop on different timescales. This sits squarely inside your standing interest in continuous, pose-estimation-based behavioral quantification rather than per-trial outcomes, and offers a conceptual mirror for the mouse work: it's a reminder that a subject can show clear neural sensitivity to a sound sequence's structure well before that sensitivity is expressed in structured movement — relevant when interpreting mice that discriminate the target sequence from its reordered distractor in evoked activity but haven't yet generalized that to a reliable licking response, especially under the currently-running slow-pacing protocol.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Effect of tempo on newborns' neural processing of auditory rhythm: Emergence of sensitivity to metrical structure</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Edalati, M. et al.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sahar Moghimi</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>University of Picardie Jules Verne</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.07.736947</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Newborns show neural sensitivity not just to a repeating auditory beat but to the slower beat-grouping periodicities (pairs or triples of beats forming a metrical hierarchy), and critically this hierarchical sensitivity only emerges at some tempi and not others, suggesting the immature auditory system has tempo-dependent limits on how much temporal structure it can extract at once. This is a direct developmental precedent for your own chord-sequence-in-stream work: your target sequence is itself a small hierarchy (a fixed 3-4 element chunk that must be detected regardless of surrounding context), and this paper's tempo-dependent breakdown of grouping sensitivity is a concrete reason to ask whether your own chord duration and inter-chord interval (150 ms/150 ms) sit inside or outside the window where a naive listener (or a mouse early in training) could extract hierarchical structure at all before learning kicks in.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medial prefrontal cortex encodes but is not required to generate goal-directed actions under threat.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Muhammad S Sajid et al.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Manuel A. Castro-Alamancos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42417528/</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Using fiber photometry, single-cell calcium imaging, and optogenetic inhibition in mouse medial prefrontal cortex during a learned avoidance task, the authors show that a large share of apparent task-related activity in this region is actually shared with a control, non-task cortical area once movement and arousal are properly regressed out, and that silencing the mPFC GABAergic neurons with the cleanest encoding of demanding avoidance contingencies had almost no effect on learning or performance. This is a direct methodological caution for your prelimbic cortex recordings during the mouse sequence-discrimination task: it argues for validating any decision-window encoding you find in prelimbic cortex against a control region and, where possible, an optogenetic perturbation, before treating anticipatory discrimination signals as causally load-bearing rather than a correlate of behavioral state.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A corticostriatal circuit updates subjective beliefs about latent task states</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Margaret L. DeMaegd et al.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Christine M. Constantinople</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.03.12.711369</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Behavioral &amp; computational modeling</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Projection-specific recordings and optogenetic perturbations from orbitofrontal neurons projecting to the caudoputamen in rats performing a hidden-reward-state task show that this corticostriatal pathway encodes categorical evidence for a latent state and that downstream neurons could in principle decode the animal's full belief distribution over states as it deliberates, giving a circuit-level implementation of belief updating about an abstract, non-observable variable. This is the closest circuit-level precedent I've seen for what your own GLM Module C (slow drifts in strategy from satiety or time-on-task) is trying to capture behaviorally: it suggests a concrete corticostriatal locus you could look to, or at least borrow the belief-decoding logic from, if you ever want to move Module C from a behavioral drift term into a claim about what a specific circuit is representing.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Visual working memory guides attention rhythmically in humans.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jiachen Lu et al.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Xilin Zhang</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>South China Normal University</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42418336/</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Rather than one or many working-memory items being simultaneously available as an attentional template, this paper finds that two remembered items alternately dominate behavioral guidance at a theta rhythm (4-8 Hz), with frontal theta phase leading the occipital alpha oscillation that tracks which item is currently prioritized. If template-guided attention is intrinsically rhythmic rather than continuously available, it's worth asking whether hit/miss timing in your human chunk-in-stream detection task shows periodicity locked to either the stimulus tempo or an endogenous rhythm, which would suggest the memorized target template is only intermittently 'online' for comparison against the incoming stream rather than being a static comparison signal.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C1q and immunoglobulins mediate activity-dependent synapse loss in the adult brain</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Beth Stevens</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.science.org/doi/abs/10.1126/science.adv1219?af=R</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Other notable</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>This Science paper (with an accompanying perspective piece, 'Antibodies sculpt adult brain circuits') shows that neuronal hyperactivity triggers region-specific deposition of complement protein C1q, and that B-lymphocyte-lineage cells and immunoglobulins are required for this activity-dependent synapse elimination in the adult hippocampus, extending complement-mediated pruning (previously known mainly from development and disease) into ongoing, activity-driven circuit refinement in the healthy adult brain. It sits well outside your auditory/sequence paradigm, but it is a field-defining mechanistic result about how immune signaling gates activity-dependent circuit remodeling, which is the same general class of question (what determines which synapses survive experience-driven plasticity) that sits underneath the auditory-cortex critical-period literature already in your canon list.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2904,7 +2904,6 @@
           <t>Newborns show neural sensitivity not just to a repeating auditory beat but to the slower beat-grouping periodicities (pairs or triples of beats forming a metrical hierarchy), and critically this hierarchical sensitivity only emerges at some tempi and not others, suggesting the immature auditory system has tempo-dependent limits on how much temporal structure it can extract at once. This is a direct developmental precedent for your own chord-sequence-in-stream work: your target sequence is itself a small hierarchy (a fixed 3-4 element chunk that must be detected regardless of surrounding context), and this paper's tempo-dependent breakdown of grouping sensitivity is a concrete reason to ask whether your own chord duration and inter-chord interval (150 ms/150 ms) sit inside or outside the window where a naive listener (or a mouse early in training) could extract hierarchical structure at all before learning kicks in.</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>No</t>
@@ -2972,7 +2971,6 @@
           <t>Using fiber photometry, single-cell calcium imaging, and optogenetic inhibition in mouse medial prefrontal cortex during a learned avoidance task, the authors show that a large share of apparent task-related activity in this region is actually shared with a control, non-task cortical area once movement and arousal are properly regressed out, and that silencing the mPFC GABAergic neurons with the cleanest encoding of demanding avoidance contingencies had almost no effect on learning or performance. This is a direct methodological caution for your prelimbic cortex recordings during the mouse sequence-discrimination task: it argues for validating any decision-window encoding you find in prelimbic cortex against a control region and, where possible, an optogenetic perturbation, before treating anticipatory discrimination signals as causally load-bearing rather than a correlate of behavioral state.</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>No</t>
@@ -3015,7 +3013,6 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>2026</t>
@@ -3036,7 +3033,6 @@
           <t>Projection-specific recordings and optogenetic perturbations from orbitofrontal neurons projecting to the caudoputamen in rats performing a hidden-reward-state task show that this corticostriatal pathway encodes categorical evidence for a latent state and that downstream neurons could in principle decode the animal's full belief distribution over states as it deliberates, giving a circuit-level implementation of belief updating about an abstract, non-observable variable. This is the closest circuit-level precedent I've seen for what your own GLM Module C (slow drifts in strategy from satiety or time-on-task) is trying to capture behaviorally: it suggests a concrete corticostriatal locus you could look to, or at least borrow the belief-decoding logic from, if you ever want to move Module C from a behavioral drift term into a claim about what a specific circuit is representing.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>No</t>
@@ -3104,7 +3100,6 @@
           <t>Rather than one or many working-memory items being simultaneously available as an attentional template, this paper finds that two remembered items alternately dominate behavioral guidance at a theta rhythm (4-8 Hz), with frontal theta phase leading the occipital alpha oscillation that tracks which item is currently prioritized. If template-guided attention is intrinsically rhythmic rather than continuously available, it's worth asking whether hit/miss timing in your human chunk-in-stream detection task shows periodicity locked to either the stimulus tempo or an endogenous rhythm, which would suggest the memorized target template is only intermittently 'online' for comparison against the incoming stream rather than being a static comparison signal.</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>No</t>
@@ -3127,7 +3122,6 @@
           <t>C1q and immunoglobulins mediate activity-dependent synapse loss in the adult brain</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>Beth Stevens</t>
@@ -3168,13 +3162,424 @@
           <t>This Science paper (with an accompanying perspective piece, 'Antibodies sculpt adult brain circuits') shows that neuronal hyperactivity triggers region-specific deposition of complement protein C1q, and that B-lymphocyte-lineage cells and immunoglobulins are required for this activity-dependent synapse elimination in the adult hippocampus, extending complement-mediated pruning (previously known mainly from development and disease) into ongoing, activity-driven circuit refinement in the healthy adult brain. It sits well outside your auditory/sequence paradigm, but it is a field-defining mechanistic result about how immune signaling gates activity-dependent circuit remodeling, which is the same general class of question (what determines which synapses survive experience-driven plasticity) that sits underneath the auditory-cortex critical-period literature already in your canon list.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Neural mechanisms of time-forward predictions for naturalistic auditory tone sequences.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Thomas J Baumgarten et al.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Biyu J He</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>New York University Langone Health</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42426016/</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>★ Paper of the Day</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Using intracranial EEG in neurosurgical patients listening to naturalistic auditory tone sequences (not the simple, artificial regularities most prediction studies use), the authors show that prediction signals are carried mainly by low-frequency activity distributed across sensory, parietal, and frontal cortex, while prediction-error signals appear in both low- and high-frequency activity, with the high-frequency component confined to sensory areas. Contrary to the common assumption that predictions and prediction errors occupy cleanly separate cortical territories or frequency bands, the two signal types overlapped substantially in both space and spectral content — a direct challenge to treating 'prediction' and 'prediction error' as spatially or spectrally segregated processes. Directed connectivity between regions decreased over the course of a sequence as its statistical structure became more predictable, except for pathways originating in parietal cortex, which stayed high — implicating parietal cortex and the dorsal auditory pathway as a sustained source of top-down predictive control rather than a passive recipient of feedforward input. Because the stimuli were naturalistic tone sequences with realistic statistical regularities rather than a simple repeating pattern, this is one of the closest published intracranial-EEG analogues to the kind of prediction your mice must be forming as they listen through a distractor-embedded chord sequence toward the target.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Impact of Education and Music Training on the Development of Abstract Thinking in the First Years of Schooling</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Théo Morfoisse et al.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Stanislas Dehaene</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Collège de France</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Open Mind</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1162/opmi.a.354</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Testing 528 children aged 4-8 on how they encode and compress auditory tone sequences and visual patterns, this paper finds that by first grade children already compress sequences using a 'Language of Thought'-style symbolic code similar to adults, with no additional benefit from several years of violin training. Because your human chunk-in-stream task is explicitly probing the transition between unconscious statistical extraction and conscious template-based chunking, this is a useful adjacent data point: it suggests the capacity to compress an auditory sequence into a compact symbolic chunk is already largely in place early in development and isn't obviously trained by musical experience, which bears on how you'd interpret individual differences in chunking ability as reflecting a fixed capacity rather than acquired expertise.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Temporal dynamics of contextual processing in the inferior colliculus of a rat model of autism: Sex- and age-dependent trajectories</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>S. Cacciato-Salcedo et al.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>M.S. Malmierca</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>University of Salamanca</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hearing Research</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.heares.2026.109659</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Using oddball and cascading paradigms in the non-lemniscal inferior colliculus, this paper cleanly dissociates three components of context-dependent auditory processing — mismatch response, repetition suppression, and prediction error — and shows they mature on different, sex-dependent trajectories, with prenatal valproic-acid exposure disrupting the pattern. This is useful groundwork for your mouse sequence-discrimination task: it demonstrates that 'prediction error' in the auditory pathway is not monolithic even at the earliest subcortical stage, worth keeping in mind when you interpret prediction-error-like modulation in your prelimbic or auditory cortex recordings as a single mechanism rather than a mixture of adaptation and genuine prediction. The cascade-plus-oddball design is also a clean methodological template if you ever want a repetition-suppression control condition for your target-versus-distractor comparisons.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Predictive acoustical processing in human cortical layers</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lonike K. Faes et al.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Federico De Martino</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Maastricht University</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41467-026-73540-z</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Using laminar-resolution fMRI during a cascading oddball paradigm, this paper localizes prediction-violation signals to superficial layers of the planum polare and middle layers of lateral temporal cortex, while model-updating signals appear in deep layers — a layer-specific dissociation that maps predictive-coding theory onto measurable human cortical architecture. This directly complements today's Paper of the Day and gives you a concrete, testable layer-based hypothesis for your own auditory-cortex recordings: if you ever get depth information from your Neuropixels probes, this predicts that prediction-error-like responses to an unexpected chord should arise more superficially than the slower model-updating signal that follows it.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The effects and interactions of top-down influences on word recognition</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Reuben Chaudhuri et al.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jan Schnupp</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hearing Research</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.heares.2026.109676</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Language, stroke &amp; BCI</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>In an EEG study of spoken-word recognition in noise, this paper separates two sources of top-down expectation — informative semantic hints versus simple stimulus repetition — and finds they operate on different timescales: hint effects fade quickly across repetition blocks while repetition-based facilitation is stronger and more persistent, dominating when both cues are present together. This maps onto the same statistical-learning-versus-template-matching distinction you use to frame your own work: the finding that repetition-based learning outlasts and overrides hint-based expectation is a concrete precedent for expecting unconscious pattern extraction to dominate over conscious template matching once a sequence has been heard enough times, directly testable across your task's five-stage difficulty progression.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Age-related changes in behavioural and neural variability in a decision-making task</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fenying Zang et al.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Anne E. Urai</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Leiden University</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41467-026-74227-1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Using more than 18,000 single units recorded across 16 brain regions — including striatum, midbrain, and thalamus alongside cortex — via the International Brain Laboratory's standardized visual decision-making task, this paper shows that ageing increases post-stimulus neural variability and reduces 'variability quenching' (the drop in trial-to-trial variability that normally follows stimulus onset), most strongly in visual and motor cortex, striatum, and thalamus. This is a direct empirical instance of treating neural variability itself, not just mean firing rate, as the target of analysis — the same spirit as your GLM's Module C for slow drifts in strategy from satiety or time-on-task. Here the 'drift' is across age rather than within a session, but the analytic move of quantifying how tightly a population's activity is quenched by a stimulus versus left noisy is directly portable to asking whether your prelimbic or auditory-cortex populations show session-long changes in variability quenching as mice gain experience with the target sequence.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3301,7 +3301,6 @@
           <t>Testing 528 children aged 4-8 on how they encode and compress auditory tone sequences and visual patterns, this paper finds that by first grade children already compress sequences using a 'Language of Thought'-style symbolic code similar to adults, with no additional benefit from several years of violin training. Because your human chunk-in-stream task is explicitly probing the transition between unconscious statistical extraction and conscious template-based chunking, this is a useful adjacent data point: it suggests the capacity to compress an auditory sequence into a compact symbolic chunk is already largely in place early in development and isn't obviously trained by musical experience, which bears on how you'd interpret individual differences in chunking ability as reflecting a fixed capacity rather than acquired expertise.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>No</t>
@@ -3369,7 +3368,6 @@
           <t>Using oddball and cascading paradigms in the non-lemniscal inferior colliculus, this paper cleanly dissociates three components of context-dependent auditory processing — mismatch response, repetition suppression, and prediction error — and shows they mature on different, sex-dependent trajectories, with prenatal valproic-acid exposure disrupting the pattern. This is useful groundwork for your mouse sequence-discrimination task: it demonstrates that 'prediction error' in the auditory pathway is not monolithic even at the earliest subcortical stage, worth keeping in mind when you interpret prediction-error-like modulation in your prelimbic or auditory cortex recordings as a single mechanism rather than a mixture of adaptation and genuine prediction. The cascade-plus-oddball design is also a clean methodological template if you ever want a repetition-suppression control condition for your target-versus-distractor comparisons.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>No</t>
@@ -3437,7 +3435,6 @@
           <t>Using laminar-resolution fMRI during a cascading oddball paradigm, this paper localizes prediction-violation signals to superficial layers of the planum polare and middle layers of lateral temporal cortex, while model-updating signals appear in deep layers — a layer-specific dissociation that maps predictive-coding theory onto measurable human cortical architecture. This directly complements today's Paper of the Day and gives you a concrete, testable layer-based hypothesis for your own auditory-cortex recordings: if you ever get depth information from your Neuropixels probes, this predicts that prediction-error-like responses to an unexpected chord should arise more superficially than the slower model-updating signal that follows it.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>No</t>
@@ -3505,7 +3502,6 @@
           <t>In an EEG study of spoken-word recognition in noise, this paper separates two sources of top-down expectation — informative semantic hints versus simple stimulus repetition — and finds they operate on different timescales: hint effects fade quickly across repetition blocks while repetition-based facilitation is stronger and more persistent, dominating when both cues are present together. This maps onto the same statistical-learning-versus-template-matching distinction you use to frame your own work: the finding that repetition-based learning outlasts and overrides hint-based expectation is a concrete precedent for expecting unconscious pattern extraction to dominate over conscious template matching once a sequence has been heard enough times, directly testable across your task's five-stage difficulty progression.</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>No</t>
@@ -3573,13 +3569,488 @@
           <t>Using more than 18,000 single units recorded across 16 brain regions — including striatum, midbrain, and thalamus alongside cortex — via the International Brain Laboratory's standardized visual decision-making task, this paper shows that ageing increases post-stimulus neural variability and reduces 'variability quenching' (the drop in trial-to-trial variability that normally follows stimulus onset), most strongly in visual and motor cortex, striatum, and thalamus. This is a direct empirical instance of treating neural variability itself, not just mean firing rate, as the target of analysis — the same spirit as your GLM's Module C for slow drifts in strategy from satiety or time-on-task. Here the 'drift' is across age rather than within a session, but the analytic move of quantifying how tightly a population's activity is quenched by a stimulus versus left noisy is directly portable to asking whether your prelimbic or auditory-cortex populations show session-long changes in variability quenching as mice gain experience with the target sequence.</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Parvalbumin and somatostatin interneurons support distinct computations during auditory scene analysis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Qu, Z. et al.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Howard Gritton</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>University of Illinois Urbana-Champaign</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.08.736456</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Using a cocktail-party-style paradigm with cell-type-specific optogenetic suppression in awake mouse auditory cortex, this preprint dissociates two interneuron classes: parvalbumin (PV) neurons broadly reshape spatial receptive-field structure (tuning width, centroid, sparseness) and support target discriminability even without any competing sound, whereas somatostatin (SST) neurons leave spatial tuning largely intact but are selectively required for discriminating a target once a spatially separated masking sound is present. This is a direct circuit-level precedent for how inhibitory interneuron subtypes in auditory cortex could differentially shape the representation of your trained target sequence versus a distractor sequence before the signal is available for a licking decision, and it's worth asking whether an analogous split exists for your temporal (rather than spatial) form of scene segregation once you extend recordings from prelimbic cortex into auditory cortex.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Auditory Streaming and Interoception</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>John Veillette et al.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Howard Nusbaum</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>University of Chicago</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UC San Diego</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.82901/nemar.on007895.v1.0.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>This is a newly deposited dataset (not a findings paper) combining behavioural auditory-streaming judgments with electrophysiological recordings of interoceptive signals, aimed at testing how internal bodily state influences auditory perceptual grouping. It's a resource worth knowing about rather than a result to cite, but the framing question, whether an internal physiological state variable modulates how a listener parses a sound stream into objects, is a useful analogy for your own GLM Module C, which tries to capture slow internal-state drift (satiety, time-on-task) shaping sequence-discrimination performance session to session.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Selective Neural Responses to Conspecific Vocalizations in Marmoset Area 32.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kevin D Johnston et al.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Kevin D Johnston</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>University of Western Ontario</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42431832/</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Auditory &amp; prefrontal electrophysiology</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Recording single units with Neuropixels and Utah arrays in marmoset pregenual anterior cingulate cortex (area 32) during playback of marmoset, macaque, human, and non-vocal sounds, this study found that 21% of 1,713 recorded neurons were categorically selective, with the strongest and earliest responses (decoding above chance within 50-100 ms) to conspecific calls, and that representational similarity analysis separated marmoset calls into their own cluster distinct from other sound categories. This directly parallels your human work's core question of how frontal cortex builds categorical representations out of continuous acoustic input, and the combination of high-density single-unit recording, population decoding, and representational similarity analysis is essentially the same analysis toolkit used in your lab's prior single-neuron finding that prefrontal cortex carries semantic rather than purely acoustic/phonological structure.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Temporal dynamics of contextual processing in the inferior colliculus of a rat model of autism: Sex- and age-dependent trajectories</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>S. Cacciato-Salcedo et al.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Manuel S. Malmierca</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>University of Salamanca</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hearing Research</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.heares.2026.109659</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Recording in the inferior colliculus of rats, this study from Malmierca's group found that normal maturation reorganizes prediction-error signalling and repetition suppression in a sex-specific way, with females developing longer response latencies and stronger prediction-driven responses, while prenatal exposure to a chemical autism model selectively disrupted this developmental trajectory in females. It's a reminder that the prediction-error/oddball framework underlying your own interest in deviance detection and regularity extraction is already known to vary by sex and developmental stage at the subcortical stage of the auditory pathway, upstream of the cortical regions you record from, which is worth keeping in mind when interpreting session-to-session or animal-to-animal variability in your own auditory-cortex data.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>When vision listens: auditory predictive processing in primary visual cortex of anesthetized rats</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jazmín S. Sánchez et al.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Manuel S. Malmierca</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>University of Salamanca</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hearing Research</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.heares.2026.109743</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Statistical learning &amp; oddball</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Also from Malmierca's group, this study recorded primary visual cortex in anesthetized rats during auditory oddball sequences and found that infragranular layers V-VI carry genuine prediction-error signals (stronger to deviant than standard tones, amplified under temporally uncertain conditions) rather than simple repetition suppression, with layer V faster/phasic and layer VI broader/sustained. It extends the predictive-coding, deviance-detection framework you draw on for your own oddball/regularity-extraction interest outside the auditory pathway entirely, which is useful context for how domain-general (versus auditory-specific) you should expect any prediction-error signal you find in prelimbic or auditory cortex to be.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Dynamic acoustic-to-categorical representations of phonemes and prosody along ventral and dorsal speech streams.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Seung-Cheol Baek et al.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Daniela Sammler</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Max Planck Institute for Empirical Aesthetics</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42431896/</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Language, stroke &amp; BCI</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Combining MEG with representational similarity and multivariate transfer-entropy analyses, this study found that acoustic and categorical representations of phonemes and prosody form in parallel (not serially, as traditional dual-stream models predict) along both the ventral and dorsal speech pathways, with prosody categories extending further along both streams than phoneme categories. This is a direct precedent for your human chunk-in-stream task's question of where and when a bottom-up acoustic signal becomes a top-down template-matched category, and the parallel-rather-than-serial finding is worth checking against your own high-gamma signal across the stimulus classes that extend from chords toward speech (synthetic vowels, open syllables).</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Molecularly defined auditory neuron subtypes show different vulnerabilities to noise- and age-related synaptopathy in mice.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Joy A Franco et al.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lisa V. Goodrich</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42431902/</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Using genetic labelling in mice, this study found that of the three spiral ganglion neuron subtypes carrying signal from the cochlea to the brain, one subtype (Ia) has larger post-synaptic densities and is resilient to both noise- and age-related synapse loss, while the other two (Ib/Ic) are vulnerable to noise-induced (but not age-related) synaptopathy, and that genetically reprogramming Ib/Ic neurons toward an Ia-like identity is protective. This bears directly on your mouse task's stimulus-design rationale, since your whole chord-frequency range (3-19 kHz) was chosen specifically to survive C57BL/6 progressive high-frequency hearing loss; this paper is a reminder that even within a frequency range chosen to avoid outright hearing loss, differential spiral-ganglion-neuron-subtype vulnerability to repeated sound exposure could still be a slow confound across the many chronic-recording sessions your task requires.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/state/reading_log.xlsx
+++ b/state/reading_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3636,7 +3636,6 @@
           <t>Using a cocktail-party-style paradigm with cell-type-specific optogenetic suppression in awake mouse auditory cortex, this preprint dissociates two interneuron classes: parvalbumin (PV) neurons broadly reshape spatial receptive-field structure (tuning width, centroid, sparseness) and support target discriminability even without any competing sound, whereas somatostatin (SST) neurons leave spatial tuning largely intact but are selectively required for discriminating a target once a spatially separated masking sound is present. This is a direct circuit-level precedent for how inhibitory interneuron subtypes in auditory cortex could differentially shape the representation of your trained target sequence versus a distractor sequence before the signal is available for a licking decision, and it's worth asking whether an analogous split exists for your temporal (rather than spatial) form of scene segregation once you extend recordings from prelimbic cortex into auditory cortex.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>No</t>
@@ -3704,7 +3703,6 @@
           <t>This is a newly deposited dataset (not a findings paper) combining behavioural auditory-streaming judgments with electrophysiological recordings of interoceptive signals, aimed at testing how internal bodily state influences auditory perceptual grouping. It's a resource worth knowing about rather than a result to cite, but the framing question, whether an internal physiological state variable modulates how a listener parses a sound stream into objects, is a useful analogy for your own GLM Module C, which tries to capture slow internal-state drift (satiety, time-on-task) shaping sequence-discrimination performance session to session.</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>No</t>
@@ -3772,7 +3770,6 @@
           <t>Recording single units with Neuropixels and Utah arrays in marmoset pregenual anterior cingulate cortex (area 32) during playback of marmoset, macaque, human, and non-vocal sounds, this study found that 21% of 1,713 recorded neurons were categorically selective, with the strongest and earliest responses (decoding above chance within 50-100 ms) to conspecific calls, and that representational similarity analysis separated marmoset calls into their own cluster distinct from other sound categories. This directly parallels your human work's core question of how frontal cortex builds categorical representations out of continuous acoustic input, and the combination of high-density single-unit recording, population decoding, and representational similarity analysis is essentially the same analysis toolkit used in your lab's prior single-neuron finding that prefrontal cortex carries semantic rather than purely acoustic/phonological structure.</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>No</t>
@@ -3840,7 +3837,6 @@
           <t>Recording in the inferior colliculus of rats, this study from Malmierca's group found that normal maturation reorganizes prediction-error signalling and repetition suppression in a sex-specific way, with females developing longer response latencies and stronger prediction-driven responses, while prenatal exposure to a chemical autism model selectively disrupted this developmental trajectory in females. It's a reminder that the prediction-error/oddball framework underlying your own interest in deviance detection and regularity extraction is already known to vary by sex and developmental stage at the subcortical stage of the auditory pathway, upstream of the cortical regions you record from, which is worth keeping in mind when interpreting session-to-session or animal-to-animal variability in your own auditory-cortex data.</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>No</t>
@@ -3908,7 +3904,6 @@
           <t>Also from Malmierca's group, this study recorded primary visual cortex in anesthetized rats during auditory oddball sequences and found that infragranular layers V-VI carry genuine prediction-error signals (stronger to deviant than standard tones, amplified under temporally uncertain conditions) rather than simple repetition suppression, with layer V faster/phasic and layer VI broader/sustained. It extends the predictive-coding, deviance-detection framework you draw on for your own oddball/regularity-extraction interest outside the auditory pathway entirely, which is useful context for how domain-general (versus auditory-specific) you should expect any prediction-error signal you find in prelimbic or auditory cortex to be.</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>No</t>
@@ -3976,7 +3971,6 @@
           <t>Combining MEG with representational similarity and multivariate transfer-entropy analyses, this study found that acoustic and categorical representations of phonemes and prosody form in parallel (not serially, as traditional dual-stream models predict) along both the ventral and dorsal speech pathways, with prosody categories extending further along both streams than phoneme categories. This is a direct precedent for your human chunk-in-stream task's question of where and when a bottom-up acoustic signal becomes a top-down template-matched category, and the parallel-rather-than-serial finding is worth checking against your own high-gamma signal across the stimulus classes that extend from chords toward speech (synthetic vowels, open syllables).</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>No</t>
@@ -4044,13 +4038,284 @@
           <t>Using genetic labelling in mice, this study found that of the three spiral ganglion neuron subtypes carrying signal from the cochlea to the brain, one subtype (Ia) has larger post-synaptic densities and is resilient to both noise- and age-related synapse loss, while the other two (Ib/Ic) are vulnerable to noise-induced (but not age-related) synaptopathy, and that genetically reprogramming Ib/Ic neurons toward an Ia-like identity is protective. This bears directly on your mouse task's stimulus-design rationale, since your whole chord-frequency range (3-19 kHz) was chosen specifically to survive C57BL/6 progressive high-frequency hearing loss; this paper is a reminder that even within a frequency range chosen to avoid outright hearing loss, differential spiral-ganglion-neuron-subtype vulnerability to repeated sound exposure could still be a slow confound across the many chronic-recording sessions your task requires.</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Rethinking hierarchy: the auditory system as an integrated cortical–subcortical network</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Michael Lohse et al.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Andrew J. King</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Nature Reviews Neuroscience</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41583-026-01045-1</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>★ Paper of the Day</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Synthesizes recent evidence that subcortical auditory structures — cochlear nucleus, inferior colliculus, thalamus — are not passive relays but active sites of adaptive coding, multisensory integration, and encoding of behavioral relevance and action, computations traditionally attributed to auditory cortex alone. Argues the auditory pathway is better understood as a distributed, heavily bidirectional cortical-subcortical network than as a strict feedforward hierarchy, with descending corticofugal projections continuously reshaping subcortical processing rather than subcortex simply feeding cortex. Reviews evidence that task engagement, prediction, and behavioral state modulate neural responses at early and subcortical stages, not only at cortex — directly relevant to any account of where in the pathway a predictive or statistical-learning signal first emerges. Because it synthesizes across the whole pathway rather than reporting one new dataset, it works as a map for locating whether a chord- or tone-sequence learning effect observed in auditory cortex could actually originate subcortically, or be inherited from descending cortical feedback rather than computed locally.</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Flexible neuronal participation within a reliable motor sequence</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Peng, J. et al.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Carlos Lois</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.10.737866</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Recording from HVC in zebra finches, a nucleus with precisely time-locked bursts during song production, this paper asks how individual neurons can vary their participation from rendition to rendition while the sung sequence itself stays behaviorally stereotyped. That distinction between reliable output and flexible single-neuron participation is a direct framework for asking whether trial-to-trial variability you see in prelimbic or auditory cortex during the mouse's fixed target sequence reflects noise, or a genuinely flexible population code with a stable readout. It also bears on the still-unsolved generalization question in the mouse task — whether the licked response generalizes across different preceding chords (treating one three-chord sequence as equivalent to another with a different first element) — since flexible neuron-to-position assignment, rather than a fixed neuron-to-chord mapping, is exactly the kind of substrate that could support that generalization.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Spontaneous emergence and evolution of neuronal sequences in recurrent networks</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Shuai Shao et al.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Julijana Gjorgjieva</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Technical University of Munich</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7554/elife.110718</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Chunking &amp; sequence processing</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>A recurrent spiking-network model (from a Technical University of Munich / Max Planck Institute for Brain Research group) shows that activity-dependent synaptic plasticity spontaneously produces repeating neuronal sequences, and that these sequences persist under ongoing plasticity — with individual synapses turning over even as the sequence-supporting connectivity motif is preserved — while structured input can reinforce or retrain which sequence gets stabilized. This gives a concrete mechanistic account for how a sequence representation like the mouse task's target could be maintained as a stable attractor in prelimbic or auditory cortex circuitry despite continuous synaptic plasticity, and maps onto the adaptive distractor-difficulty thermostat, where a distractor confused with the target (structured, informative input) reshapes existing connectivity rather than the representation being built from scratch. Flagged partly for local relevance: this is a Munich-based computational neuroscience group per the standing interest in the reader's local systems/computational-neuroscience community.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Simple Geometric Recentering Rivals Deep Sequence Models for Cross-Session EEG Motor-Imagery Decoding</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rahimipour, M. et al.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Marc Van Hulle</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>KU Leuven</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.07.736991</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Circuits, methods &amp; population analysis</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Benchmarks whether the added complexity of deep sequence models for cross-session EEG motor-imagery decoding is actually justified against a simple tangent-space geometric recentering baseline, across eight public datasets spanning single- and multi-session recordings — and finds the simple recentering approach rivals or beats deep models at handling session-to-session non-stationarity. This is a direct methods lesson for the human chunk-in-stream work, which needs stable decoding across the seven recording sessions from the same chronic Utah-array implant: before reaching for a heavier cross-session alignment architecture, it argues for first testing whether a much simpler geometric recentering step on the population activity already captures most of the achievable cross-session stability.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>No</t>
         </is>
